--- a/etf_holdings/2026-10-31_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-31_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:22</t>
+          <t>2026-10-31 22:43:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:26</t>
+          <t>2026-10-31 22:43:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:28</t>
+          <t>2026-10-31 22:43:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:29</t>
+          <t>2026-10-31 22:43:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:29</t>
+          <t>2026-10-31 22:43:31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:29</t>
+          <t>2026-10-31 22:43:31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:29</t>
+          <t>2026-10-31 22:43:31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:29</t>
+          <t>2026-10-31 22:43:31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-31 22:37:29</t>
+          <t>2026-10-31 22:43:31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-31_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-31_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:26</t>
+          <t>2026-10-31 23:18:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:29</t>
+          <t>2026-10-31 23:18:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:30</t>
+          <t>2026-10-31 23:18:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:31</t>
+          <t>2026-10-31 23:18:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:31</t>
+          <t>2026-10-31 23:18:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:31</t>
+          <t>2026-10-31 23:18:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:31</t>
+          <t>2026-10-31 23:18:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:31</t>
+          <t>2026-10-31 23:18:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-31 22:43:31</t>
+          <t>2026-10-31 23:18:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
